--- a/vse-loti/339448038/spec-339448038.xlsx
+++ b/vse-loti/339448038/spec-339448038.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +437,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +505,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -512,14 +515,14 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>24996036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Источник: 852614903.htm</t>
+          <t>Источник: 852614903.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339448038/spec-339448038.xlsx
+++ b/vse-loti/339448038/spec-339448038.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,13 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -500,27 +503,237 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>6817095</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>9089460</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>908946</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4544730</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2272365</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1136182.5</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Трубы круглого сечения прочие стальные</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>4544.73</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>5453.68</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>227236.5</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="H9" s="5" t="n">
+        <v>24996015</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H10" s="5" t="n">
         <v>24996036</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Источник: 852614903.txt</t>
         </is>

--- a/vse-loti/339448038/spec-339448038.xlsx
+++ b/vse-loti/339448038/spec-339448038.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,10 +65,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +445,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +475,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -521,16 +508,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>6817095</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -551,16 +532,10 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H3" s="3" t="n">
         <v>9089460</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -581,16 +556,10 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H4" s="3" t="n">
         <v>908946</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -611,16 +580,10 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H5" s="3" t="n">
         <v>4544730</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -641,16 +604,10 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H6" s="3" t="n">
         <v>2272365</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -671,16 +628,10 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H7" s="3" t="n">
         <v>1136182.5</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -701,16 +652,10 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>4544.73</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>5453.68</v>
-      </c>
-      <c r="H8" s="3" t="n">
         <v>227236.5</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -718,7 +663,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>24996015</v>
       </c>
     </row>
@@ -728,7 +673,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>24996036</v>
       </c>
     </row>
